--- a/output/Tables/2019/Resampling/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>372.6185665119147</v>
+        <v>627.7559219531272</v>
       </c>
       <c r="B2">
-        <v>502.8206040889954</v>
+        <v>766.0292120135045</v>
       </c>
       <c r="C2">
-        <v>814.2487031263249</v>
+        <v>1012.395218851743</v>
       </c>
       <c r="D2">
-        <v>0.2664222750560195</v>
+        <v>0.4488454841964872</v>
       </c>
       <c r="E2">
-        <v>0.3595167319236321</v>
+        <v>0.5477108865896573</v>
       </c>
       <c r="F2">
-        <v>0.5821878227353231</v>
+        <v>0.7238625814789984</v>
       </c>
       <c r="G2">
-        <v>3.330278438200243</v>
+        <v>5.61056855245609</v>
       </c>
       <c r="H2">
-        <v>4.493959149045401</v>
+        <v>6.846386082370716</v>
       </c>
       <c r="I2">
-        <v>7.277347784191539</v>
+        <v>9.04828226848748</v>
       </c>
       <c r="J2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/soc_1€_step_km_min_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/soc_1€_step_km_min_1000replicate.xlsx
@@ -408,31 +408,31 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>627.7559219531272</v>
+        <v>145.380042328373</v>
       </c>
       <c r="B2">
-        <v>766.0292120135045</v>
+        <v>176.7243870324087</v>
       </c>
       <c r="C2">
-        <v>1012.395218851743</v>
+        <v>231.9785360692528</v>
       </c>
       <c r="D2">
-        <v>0.4488454841964872</v>
+        <v>0.103946730264787</v>
       </c>
       <c r="E2">
-        <v>0.5477108865896573</v>
+        <v>0.1263579367281725</v>
       </c>
       <c r="F2">
-        <v>0.7238625814789984</v>
+        <v>0.1658646532895162</v>
       </c>
       <c r="G2">
-        <v>5.61056855245609</v>
+        <v>1.299334128309837</v>
       </c>
       <c r="H2">
-        <v>6.846386082370716</v>
+        <v>1.579474209102157</v>
       </c>
       <c r="I2">
-        <v>9.04828226848748</v>
+        <v>2.073308166118953</v>
       </c>
       <c r="J2">
         <v>1</v>
